--- a/data/mk_inv_data_master.xlsx
+++ b/data/mk_inv_data_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1547.38</v>
+        <v>1548.88</v>
       </c>
       <c r="F7" t="n">
         <v>1558.84</v>
@@ -687,11 +687,11 @@
         <v>1559.44</v>
       </c>
       <c r="H7" t="n">
-        <v>1547.38</v>
+        <v>1545.78</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="8">
@@ -730,34 +730,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>원/엔 환율</t>
+          <t>원/위안 환율</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9.455399999999999</v>
+        <v>228.45</v>
       </c>
       <c r="F9" t="n">
-        <v>9.454499999999999</v>
+        <v>230.48</v>
       </c>
       <c r="G9" t="n">
-        <v>9.519</v>
+        <v>230.57</v>
       </c>
       <c r="H9" t="n">
-        <v>9.416399999999999</v>
+        <v>228.35</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -778,25 +778,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9.4658</v>
+        <v>9.455399999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>9.473599999999999</v>
+        <v>9.454499999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>9.516299999999999</v>
+        <v>9.519</v>
       </c>
       <c r="H10" t="n">
-        <v>9.455500000000001</v>
+        <v>9.416399999999999</v>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>0.0011</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -814,24 +812,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.480499999999999</v>
+        <v>9.4658</v>
       </c>
       <c r="F11" t="n">
-        <v>9.485099999999999</v>
+        <v>9.473599999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>9.5998</v>
+        <v>9.516299999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>9.4712</v>
+        <v>9.455500000000001</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>0.0016</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="12">
@@ -850,24 +848,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.5656</v>
+        <v>9.480499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>9.57</v>
+        <v>9.485099999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>9.632099999999999</v>
+        <v>9.5998</v>
       </c>
       <c r="H12" t="n">
-        <v>9.519500000000001</v>
+        <v>9.4712</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="13">
@@ -886,24 +884,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.5799</v>
+        <v>9.5656</v>
       </c>
       <c r="F13" t="n">
-        <v>9.5884</v>
+        <v>9.57</v>
       </c>
       <c r="G13" t="n">
-        <v>9.714600000000001</v>
+        <v>9.632099999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>9.576599999999999</v>
+        <v>9.519500000000001</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0.0015</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -922,59 +920,61 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.647</v>
+        <v>9.5799</v>
       </c>
       <c r="F14" t="n">
-        <v>9.706</v>
+        <v>9.5884</v>
       </c>
       <c r="G14" t="n">
-        <v>9.711</v>
+        <v>9.714600000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>9.647</v>
+        <v>9.576599999999999</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>0.007</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VIX 변동성지수</t>
+          <t>원/엔 환율</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>16.05</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>15.88</v>
+        <v>9.706</v>
       </c>
       <c r="G15" t="n">
-        <v>16.34</v>
+        <v>9.711</v>
       </c>
       <c r="H15" t="n">
-        <v>15.71</v>
+        <v>9.627000000000001</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>0.0063</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -992,25 +992,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>15.77</v>
+        <v>16.05</v>
       </c>
       <c r="F16" t="n">
-        <v>16.28</v>
+        <v>15.88</v>
       </c>
       <c r="G16" t="n">
-        <v>16.29</v>
+        <v>16.34</v>
       </c>
       <c r="H16" t="n">
         <v>15.71</v>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>-0.0174</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1028,24 +1026,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16.06</v>
+        <v>15.77</v>
       </c>
       <c r="F17" t="n">
-        <v>15.97</v>
+        <v>16.28</v>
       </c>
       <c r="G17" t="n">
-        <v>16.63</v>
+        <v>16.29</v>
       </c>
       <c r="H17" t="n">
-        <v>15.94</v>
+        <v>15.71</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>0.0184</v>
+        <v>-0.0174</v>
       </c>
     </row>
     <row r="18">
@@ -1064,24 +1062,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>15.4</v>
+        <v>16.06</v>
       </c>
       <c r="F18" t="n">
-        <v>16.33</v>
+        <v>15.97</v>
       </c>
       <c r="G18" t="n">
-        <v>16.8</v>
+        <v>16.63</v>
       </c>
       <c r="H18" t="n">
-        <v>15.18</v>
+        <v>15.94</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>-0.0411</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="19">
@@ -1100,59 +1098,61 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>21.51</v>
+        <v>15.4</v>
       </c>
       <c r="F19" t="n">
-        <v>15.87</v>
+        <v>16.33</v>
       </c>
       <c r="G19" t="n">
-        <v>21.57</v>
+        <v>16.8</v>
       </c>
       <c r="H19" t="n">
-        <v>15.56</v>
+        <v>15.18</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>0.3968</v>
+        <v>-0.0411</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WTI 원유</t>
+          <t>VIX 변동성지수</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>92.16</v>
+        <v>21.51</v>
       </c>
       <c r="F20" t="n">
-        <v>88.5</v>
+        <v>15.87</v>
       </c>
       <c r="G20" t="n">
-        <v>94.78</v>
+        <v>21.57</v>
       </c>
       <c r="H20" t="n">
-        <v>88.45</v>
+        <v>15.56</v>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>0.3968</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1170,25 +1170,23 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>93.76000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="F21" t="n">
-        <v>92.45</v>
+        <v>88.5</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>94.78</v>
       </c>
       <c r="H21" t="n">
-        <v>90.12</v>
+        <v>88.45</v>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>0.0174</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1206,24 +1204,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96.02</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>93.45</v>
+        <v>92.45</v>
       </c>
       <c r="G22" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H22" t="n">
-        <v>93.45</v>
+        <v>90.12</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>0.0241</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="23">
@@ -1242,24 +1240,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93.04000000000001</v>
+        <v>96.02</v>
       </c>
       <c r="F23" t="n">
-        <v>95.75</v>
+        <v>93.45</v>
       </c>
       <c r="G23" t="n">
-        <v>95.91</v>
+        <v>97</v>
       </c>
       <c r="H23" t="n">
-        <v>91.91</v>
+        <v>93.45</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>-0.031</v>
+        <v>0.0241</v>
       </c>
     </row>
     <row r="24">
@@ -1278,24 +1276,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>90.54000000000001</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>92.81999999999999</v>
+        <v>95.75</v>
       </c>
       <c r="G24" t="n">
-        <v>93.63</v>
+        <v>95.91</v>
       </c>
       <c r="H24" t="n">
-        <v>89.68000000000001</v>
+        <v>91.91</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-0.0269</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="25">
@@ -1314,63 +1312,61 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20260607</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>92.56</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>93</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>93.90000000000001</v>
+        <v>93.63</v>
       </c>
       <c r="H25" t="n">
-        <v>92.36</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>0.0223</v>
+        <v>-0.0269</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XAU</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>금(Gold) 현물</t>
+          <t>WTI 원유</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260607</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4475.2</v>
+        <v>93.31</v>
       </c>
       <c r="F26" t="n">
-        <v>4523.5</v>
+        <v>93</v>
       </c>
       <c r="G26" t="n">
-        <v>4541.4</v>
+        <v>94.8</v>
       </c>
       <c r="H26" t="n">
-        <v>4449.7</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>92.2</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>0.0306</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1388,29 +1384,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4489.1</v>
+        <v>4475.2</v>
       </c>
       <c r="F27" t="n">
-        <v>4488</v>
+        <v>4523.5</v>
       </c>
       <c r="G27" t="n">
-        <v>4529.5</v>
+        <v>4541.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4474.2</v>
+        <v>4449.7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>0.0031</v>
-      </c>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1428,28 +1422,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4436.7</v>
+        <v>4489.1</v>
       </c>
       <c r="F28" t="n">
-        <v>4471.2</v>
+        <v>4488</v>
       </c>
       <c r="G28" t="n">
-        <v>4471.7</v>
+        <v>4529.5</v>
       </c>
       <c r="H28" t="n">
-        <v>4427.2</v>
+        <v>4474.2</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.91K</t>
+          <t>456</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-0.0117</v>
+        <v>0.0031</v>
       </c>
     </row>
     <row r="29">
@@ -1468,28 +1462,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4475.8</v>
+        <v>4436.7</v>
       </c>
       <c r="F29" t="n">
-        <v>4447.4</v>
+        <v>4471.2</v>
       </c>
       <c r="G29" t="n">
-        <v>4509.9</v>
+        <v>4471.7</v>
       </c>
       <c r="H29" t="n">
-        <v>4447.4</v>
+        <v>4427.2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>2.91K</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0117</v>
       </c>
     </row>
     <row r="30">
@@ -1508,20 +1502,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4337.1</v>
+        <v>4475.8</v>
       </c>
       <c r="F30" t="n">
-        <v>4472.3</v>
+        <v>4447.4</v>
       </c>
       <c r="G30" t="n">
-        <v>4472.3</v>
+        <v>4509.9</v>
       </c>
       <c r="H30" t="n">
-        <v>4319.1</v>
+        <v>4447.4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1529,7 +1523,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>-0.031</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1548,67 +1542,69 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20260607</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4369</v>
+        <v>4337.1</v>
       </c>
       <c r="F31" t="n">
-        <v>4354</v>
+        <v>4472.3</v>
       </c>
       <c r="G31" t="n">
-        <v>4377.5</v>
+        <v>4472.3</v>
       </c>
       <c r="H31" t="n">
-        <v>4333.4</v>
+        <v>4319.1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10.02K</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.0074</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KS11</t>
+          <t>XAU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>코스피(KOSPI) 지수</t>
+          <t>금(Gold) 현물</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260607</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>8788.379999999999</v>
+        <v>4347.8</v>
       </c>
       <c r="F32" t="n">
-        <v>8485.67</v>
+        <v>4354</v>
       </c>
       <c r="G32" t="n">
-        <v>8874.16</v>
+        <v>4377.5</v>
       </c>
       <c r="H32" t="n">
-        <v>8485.67</v>
+        <v>4323.6</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>636.20K</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>19.22K</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.0025</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1626,29 +1622,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8801.49</v>
+        <v>8788.379999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>8883.190000000001</v>
+        <v>8485.67</v>
       </c>
       <c r="G33" t="n">
-        <v>8933.620000000001</v>
+        <v>8874.16</v>
       </c>
       <c r="H33" t="n">
-        <v>8503.120000000001</v>
+        <v>8485.67</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>632.60K</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0015</v>
-      </c>
+          <t>636.20K</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1666,28 +1660,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>8639.41</v>
+        <v>8801.49</v>
       </c>
       <c r="F34" t="n">
-        <v>8623.82</v>
+        <v>8883.190000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>8759.049999999999</v>
+        <v>8933.620000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>8577.299999999999</v>
+        <v>8503.120000000001</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>437.90K</t>
+          <t>632.60K</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>-0.0184</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="35">
@@ -1706,28 +1700,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8160.59</v>
+        <v>8639.41</v>
       </c>
       <c r="F35" t="n">
-        <v>8323.200000000001</v>
+        <v>8623.82</v>
       </c>
       <c r="G35" t="n">
-        <v>8382.16</v>
+        <v>8759.049999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>8038.1</v>
+        <v>8577.299999999999</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>463.20K</t>
+          <t>437.90K</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>-0.0554</v>
+        <v>-0.0184</v>
       </c>
     </row>
     <row r="36">
@@ -1746,67 +1740,69 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>7477.46</v>
+        <v>8160.59</v>
       </c>
       <c r="F36" t="n">
-        <v>8048.09</v>
+        <v>8323.200000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>8048.09</v>
+        <v>8382.16</v>
       </c>
       <c r="H36" t="n">
-        <v>7442.73</v>
+        <v>8038.1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23.87K</t>
+          <t>463.20K</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>-0.0837</v>
+        <v>-0.0554</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KS200</t>
+          <t>KS11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>코스피200 지수</t>
+          <t>코스피(KOSPI) 지수</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1399.91</v>
+        <v>7591.56</v>
       </c>
       <c r="F37" t="n">
-        <v>1344.09</v>
+        <v>8048.09</v>
       </c>
       <c r="G37" t="n">
-        <v>1412.58</v>
+        <v>8048.09</v>
       </c>
       <c r="H37" t="n">
-        <v>1343.96</v>
+        <v>7442.73</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>339.00M</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>171.70K</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.0697</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1824,29 +1820,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1407.23</v>
+        <v>1399.91</v>
       </c>
       <c r="F38" t="n">
-        <v>1419.07</v>
+        <v>1344.09</v>
       </c>
       <c r="G38" t="n">
-        <v>1430.49</v>
+        <v>1412.58</v>
       </c>
       <c r="H38" t="n">
-        <v>1353.19</v>
+        <v>1343.96</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>318.60M</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>0.0052</v>
-      </c>
+          <t>339.00M</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1864,28 +1858,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1379.56</v>
+        <v>1407.23</v>
       </c>
       <c r="F39" t="n">
-        <v>1374.74</v>
+        <v>1419.07</v>
       </c>
       <c r="G39" t="n">
-        <v>1402.04</v>
+        <v>1430.49</v>
       </c>
       <c r="H39" t="n">
-        <v>1367.15</v>
+        <v>1353.19</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>192.90M</t>
+          <t>318.60M</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>-0.0197</v>
+        <v>0.0052</v>
       </c>
     </row>
     <row r="40">
@@ -1904,28 +1898,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1297.02</v>
+        <v>1379.56</v>
       </c>
       <c r="F40" t="n">
-        <v>1323.25</v>
+        <v>1374.74</v>
       </c>
       <c r="G40" t="n">
-        <v>1338.13</v>
+        <v>1402.04</v>
       </c>
       <c r="H40" t="n">
-        <v>1278.65</v>
+        <v>1367.15</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>199.50M</t>
+          <t>192.90M</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>-0.0598</v>
+        <v>-0.0197</v>
       </c>
     </row>
     <row r="41">
@@ -1944,67 +1938,69 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1186.44</v>
+        <v>1297.02</v>
       </c>
       <c r="F41" t="n">
-        <v>1282.81</v>
+        <v>1323.25</v>
       </c>
       <c r="G41" t="n">
-        <v>1282.81</v>
+        <v>1338.13</v>
       </c>
       <c r="H41" t="n">
-        <v>1177.72</v>
+        <v>1278.65</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10.37K</t>
+          <t>199.50M</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>-0.0853</v>
+        <v>-0.0598</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KQ11</t>
+          <t>KS200</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>코스닥(KOSDAQ) 지수</t>
+          <t>코스피200 지수</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1050.03</v>
+        <v>1205.99</v>
       </c>
       <c r="F42" t="n">
-        <v>1072.77</v>
+        <v>1282.81</v>
       </c>
       <c r="G42" t="n">
-        <v>1082.75</v>
+        <v>1282.81</v>
       </c>
       <c r="H42" t="n">
-        <v>1043.91</v>
+        <v>1177.72</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>835.00K</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>72.38K</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.0702</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2022,29 +2018,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1026.03</v>
+        <v>1050.03</v>
       </c>
       <c r="F43" t="n">
-        <v>1044.89</v>
+        <v>1072.77</v>
       </c>
       <c r="G43" t="n">
-        <v>1045.77</v>
+        <v>1082.75</v>
       </c>
       <c r="H43" t="n">
-        <v>1009.75</v>
+        <v>1043.91</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>774.80K</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>-0.0229</v>
-      </c>
+          <t>835.00K</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2062,28 +2056,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049.73</v>
+        <v>1026.03</v>
       </c>
       <c r="F44" t="n">
-        <v>1032.91</v>
+        <v>1044.89</v>
       </c>
       <c r="G44" t="n">
-        <v>1065.9</v>
+        <v>1045.77</v>
       </c>
       <c r="H44" t="n">
-        <v>1032.29</v>
+        <v>1009.75</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>623.00K</t>
+          <t>774.80K</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0.0231</v>
+        <v>-0.0229</v>
       </c>
     </row>
     <row r="45">
@@ -2102,28 +2096,28 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1002.44</v>
+        <v>1049.73</v>
       </c>
       <c r="F45" t="n">
-        <v>1035.22</v>
+        <v>1032.91</v>
       </c>
       <c r="G45" t="n">
-        <v>1035.22</v>
+        <v>1065.9</v>
       </c>
       <c r="H45" t="n">
-        <v>992.8</v>
+        <v>1032.29</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>724.40K</t>
+          <t>623.00K</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>-0.045</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="46">
@@ -2142,67 +2136,69 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>935.77</v>
+        <v>1002.44</v>
       </c>
       <c r="F46" t="n">
-        <v>959.61</v>
+        <v>1035.22</v>
       </c>
       <c r="G46" t="n">
-        <v>959.61</v>
+        <v>1035.22</v>
       </c>
       <c r="H46" t="n">
-        <v>924.53</v>
+        <v>992.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>141.58K</t>
+          <t>724.40K</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>-0.0665</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>KQ11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>다우존스 산업평균지수</t>
+          <t>코스닥(KOSDAQ) 지수</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>51078.88</v>
+        <v>928.6799999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>51161.1</v>
+        <v>959.61</v>
       </c>
       <c r="G47" t="n">
-        <v>51161.1</v>
+        <v>959.61</v>
       </c>
       <c r="H47" t="n">
-        <v>50767.32</v>
+        <v>924.53</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>625.19M</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>299.69K</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>-0.0736</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2220,29 +2216,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>51307.79</v>
+        <v>51078.88</v>
       </c>
       <c r="F48" t="n">
-        <v>50912.84</v>
+        <v>51161.1</v>
       </c>
       <c r="G48" t="n">
-        <v>51369.61</v>
+        <v>51161.1</v>
       </c>
       <c r="H48" t="n">
-        <v>50829.55</v>
+        <v>50767.32</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>548.76M</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>0.0045</v>
-      </c>
+          <t>625.19M</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2260,28 +2254,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>50687.07</v>
+        <v>51307.79</v>
       </c>
       <c r="F49" t="n">
-        <v>51220.92</v>
+        <v>50912.84</v>
       </c>
       <c r="G49" t="n">
-        <v>51220.92</v>
+        <v>51369.61</v>
       </c>
       <c r="H49" t="n">
-        <v>50687.07</v>
+        <v>50829.55</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>546.85M</t>
+          <t>548.76M</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>-0.0121</v>
+        <v>0.0045</v>
       </c>
     </row>
     <row r="50">
@@ -2300,28 +2294,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51561.93</v>
+        <v>50687.07</v>
       </c>
       <c r="F50" t="n">
-        <v>50986.1</v>
+        <v>51220.92</v>
       </c>
       <c r="G50" t="n">
-        <v>51657.89</v>
+        <v>51220.92</v>
       </c>
       <c r="H50" t="n">
-        <v>50986.1</v>
+        <v>50687.07</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>520.67M</t>
+          <t>546.85M</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0.0173</v>
+        <v>-0.0121</v>
       </c>
     </row>
     <row r="51">
@@ -2340,63 +2334,69 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>50866.78</v>
+        <v>51561.93</v>
       </c>
       <c r="F51" t="n">
-        <v>51610.02</v>
+        <v>50986.1</v>
       </c>
       <c r="G51" t="n">
-        <v>51660.4</v>
+        <v>51657.89</v>
       </c>
       <c r="H51" t="n">
-        <v>50781.45</v>
+        <v>50986.1</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>638.68M</t>
+          <t>520.67M</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>-0.0135</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SP500(SPX)</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>S&amp;P500 지수</t>
+          <t>다우존스 산업평균지수</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>7599.96</v>
+        <v>50866.78</v>
       </c>
       <c r="F52" t="n">
-        <v>7582.29</v>
+        <v>51610.02</v>
       </c>
       <c r="G52" t="n">
-        <v>7617.66</v>
+        <v>51660.4</v>
       </c>
       <c r="H52" t="n">
-        <v>7562.61</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+        <v>50781.45</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>638.68M</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>-0.0135</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2414,25 +2414,23 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>7609.78</v>
+        <v>7599.96</v>
       </c>
       <c r="F53" t="n">
-        <v>7595.4</v>
+        <v>7582.29</v>
       </c>
       <c r="G53" t="n">
-        <v>7620.9</v>
+        <v>7617.66</v>
       </c>
       <c r="H53" t="n">
-        <v>7582.99</v>
+        <v>7562.61</v>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="n">
-        <v>0.0013</v>
-      </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2450,24 +2448,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7553.68</v>
+        <v>7609.78</v>
       </c>
       <c r="F54" t="n">
-        <v>7605.31</v>
+        <v>7595.4</v>
       </c>
       <c r="G54" t="n">
-        <v>7605.35</v>
+        <v>7620.9</v>
       </c>
       <c r="H54" t="n">
-        <v>7551.22</v>
+        <v>7582.99</v>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>-0.0074</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="55">
@@ -2486,24 +2484,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7584.31</v>
+        <v>7553.68</v>
       </c>
       <c r="F55" t="n">
-        <v>7516.54</v>
+        <v>7605.31</v>
       </c>
       <c r="G55" t="n">
-        <v>7598.19</v>
+        <v>7605.35</v>
       </c>
       <c r="H55" t="n">
-        <v>7516.54</v>
+        <v>7551.22</v>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>0.0041</v>
+        <v>-0.0074</v>
       </c>
     </row>
     <row r="56">
@@ -2522,63 +2520,61 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>7383.74</v>
+        <v>7584.31</v>
       </c>
       <c r="F56" t="n">
-        <v>7537.36</v>
+        <v>7516.54</v>
       </c>
       <c r="G56" t="n">
-        <v>7541.81</v>
+        <v>7598.19</v>
       </c>
       <c r="H56" t="n">
-        <v>7368.63</v>
+        <v>7516.54</v>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>-0.0264</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NASDAQ(IXIC)</t>
+          <t>SP500(SPX)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>나스닥 종합지수</t>
+          <t>S&amp;P500 지수</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>27086.81</v>
+        <v>7383.74</v>
       </c>
       <c r="F57" t="n">
-        <v>26952.58</v>
+        <v>7537.36</v>
       </c>
       <c r="G57" t="n">
-        <v>27190.21</v>
+        <v>7541.81</v>
       </c>
       <c r="H57" t="n">
-        <v>26913.12</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10.20B</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>7368.63</v>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>-0.0264</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2596,29 +2592,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>27093.9</v>
+        <v>27086.81</v>
       </c>
       <c r="F58" t="n">
-        <v>27030.07</v>
+        <v>26952.58</v>
       </c>
       <c r="G58" t="n">
-        <v>27171.29</v>
+        <v>27190.21</v>
       </c>
       <c r="H58" t="n">
-        <v>26932.77</v>
+        <v>26913.12</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>9.68B</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>0.0003</v>
-      </c>
+          <t>10.20B</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2636,28 +2630,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>26853.98</v>
+        <v>27093.9</v>
       </c>
       <c r="F59" t="n">
-        <v>27092.85</v>
+        <v>27030.07</v>
       </c>
       <c r="G59" t="n">
-        <v>27130.88</v>
+        <v>27171.29</v>
       </c>
       <c r="H59" t="n">
-        <v>26769.15</v>
+        <v>26932.77</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>9.27B</t>
+          <t>9.68B</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>-0.0089</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="60">
@@ -2676,28 +2670,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>26830.96</v>
+        <v>26853.98</v>
       </c>
       <c r="F60" t="n">
-        <v>26579.3</v>
+        <v>27092.85</v>
       </c>
       <c r="G60" t="n">
-        <v>26923.7</v>
+        <v>27130.88</v>
       </c>
       <c r="H60" t="n">
-        <v>26554.24</v>
+        <v>26769.15</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>9.00B</t>
+          <t>9.27B</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>-0.0009</v>
+        <v>-0.0089</v>
       </c>
     </row>
     <row r="61">
@@ -2716,63 +2710,69 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>25709.43</v>
+        <v>26830.96</v>
       </c>
       <c r="F61" t="n">
-        <v>26536.59</v>
+        <v>26579.3</v>
       </c>
       <c r="G61" t="n">
-        <v>26572.25</v>
+        <v>26923.7</v>
       </c>
       <c r="H61" t="n">
-        <v>25648.47</v>
+        <v>26554.24</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>11.55B</t>
+          <t>9.00B</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>-0.0418</v>
+        <v>-0.0009</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>NASDAQ(IXIC)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>필라델피아 반도체지수</t>
+          <t>나스닥 종합지수</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>12965.65</v>
+        <v>25709.43</v>
       </c>
       <c r="F62" t="n">
-        <v>12706.62</v>
+        <v>26536.59</v>
       </c>
       <c r="G62" t="n">
-        <v>13088.01</v>
+        <v>26572.25</v>
       </c>
       <c r="H62" t="n">
-        <v>12631.03</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+        <v>25648.47</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11.55B</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>-0.0418</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2790,25 +2790,23 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>13726.27</v>
+        <v>12965.65</v>
       </c>
       <c r="F63" t="n">
-        <v>13242.7</v>
+        <v>12706.62</v>
       </c>
       <c r="G63" t="n">
-        <v>13733.72</v>
+        <v>13088.01</v>
       </c>
       <c r="H63" t="n">
-        <v>13202.18</v>
+        <v>12631.03</v>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="n">
-        <v>0.0587</v>
-      </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2826,24 +2824,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>13916.96</v>
+        <v>13726.27</v>
       </c>
       <c r="F64" t="n">
-        <v>13971.15</v>
+        <v>13242.7</v>
       </c>
       <c r="G64" t="n">
-        <v>13998.14</v>
+        <v>13733.72</v>
       </c>
       <c r="H64" t="n">
-        <v>13554.37</v>
+        <v>13202.18</v>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>0.0139</v>
+        <v>0.0587</v>
       </c>
     </row>
     <row r="65">
@@ -2862,24 +2860,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>13617.5</v>
+        <v>13916.96</v>
       </c>
       <c r="F65" t="n">
-        <v>13243.66</v>
+        <v>13971.15</v>
       </c>
       <c r="G65" t="n">
-        <v>13819.62</v>
+        <v>13998.14</v>
       </c>
       <c r="H65" t="n">
-        <v>13041.28</v>
+        <v>13554.37</v>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>-0.0215</v>
+        <v>0.0139</v>
       </c>
     </row>
     <row r="66">
@@ -2898,23 +2896,59 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12220.76</v>
+        <v>13617.5</v>
       </c>
       <c r="F66" t="n">
-        <v>13062.55</v>
+        <v>13243.66</v>
       </c>
       <c r="G66" t="n">
-        <v>13111.44</v>
+        <v>13819.62</v>
       </c>
       <c r="H66" t="n">
-        <v>12217.32</v>
+        <v>13041.28</v>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
+        <v>-0.0215</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>19</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SOX</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>필라델피아 반도체지수</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>12220.76</v>
+      </c>
+      <c r="F67" t="n">
+        <v>13062.55</v>
+      </c>
+      <c r="G67" t="n">
+        <v>13111.44</v>
+      </c>
+      <c r="H67" t="n">
+        <v>12217.32</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="n">
         <v>-0.1026</v>
       </c>
     </row>

--- a/data/mk_inv_data_master.xlsx
+++ b/data/mk_inv_data_master.xlsx
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1515.46</v>
+        <v>1512.61</v>
       </c>
       <c r="F29" t="n">
         <v>1526.82</v>
@@ -1479,11 +1479,11 @@
         <v>1533.02</v>
       </c>
       <c r="H29" t="n">
-        <v>1513.68</v>
+        <v>1508.98</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>-0.0251</v>
+        <v>-0.0269</v>
       </c>
     </row>
     <row r="30">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223.58</v>
+        <v>223.51</v>
       </c>
       <c r="F31" t="n">
         <v>225.83</v>
@@ -1549,7 +1549,7 @@
         <v>225.99</v>
       </c>
       <c r="H31" t="n">
-        <v>223.51</v>
+        <v>223.07</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>9.433</v>
+        <v>9.426</v>
       </c>
       <c r="F59" t="n">
         <v>9.512</v>
@@ -2553,11 +2553,11 @@
         <v>9.547000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>9.433</v>
+        <v>9.407999999999999</v>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>-0.0268</v>
+        <v>-0.0276</v>
       </c>
     </row>
     <row r="60">
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>90.15000000000001</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="F114" t="n">
         <v>91.28</v>
@@ -4529,11 +4529,11 @@
         <v>91.55</v>
       </c>
       <c r="H114" t="n">
-        <v>89.84999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>-0.0126</v>
+        <v>-0.0174</v>
       </c>
     </row>
     <row r="115">
@@ -5634,24 +5634,24 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4355.6</v>
+        <v>4367.3</v>
       </c>
       <c r="F142" t="n">
         <v>4354.7</v>
       </c>
       <c r="G142" t="n">
-        <v>4366.5</v>
+        <v>4375.7</v>
       </c>
       <c r="H142" t="n">
         <v>4336</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>17.62K</t>
+          <t>21.53K</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>0.0045</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="143">
@@ -9286,24 +9286,24 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>8047.71</v>
+        <v>8064.01</v>
       </c>
       <c r="F241" t="n">
         <v>7697.76</v>
       </c>
       <c r="G241" t="n">
-        <v>8086.47</v>
+        <v>8119.09</v>
       </c>
       <c r="H241" t="n">
         <v>7598.87</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>357.15K</t>
+          <t>415.32K</t>
         </is>
       </c>
       <c r="J241" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="242">
@@ -10244,24 +10244,24 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>1283.04</v>
+        <v>1287.25</v>
       </c>
       <c r="F265" t="n">
         <v>1221.75</v>
       </c>
       <c r="G265" t="n">
-        <v>1290.59</v>
+        <v>1297.79</v>
       </c>
       <c r="H265" t="n">
         <v>1206.94</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>157.10K</t>
+          <t>185.58K</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>0.0813</v>
+        <v>0.0849</v>
       </c>
     </row>
     <row r="266">
@@ -11202,24 +11202,24 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>979.63</v>
+        <v>965.79</v>
       </c>
       <c r="F289" t="n">
         <v>937.6900000000001</v>
       </c>
       <c r="G289" t="n">
-        <v>979.63</v>
+        <v>981.24</v>
       </c>
       <c r="H289" t="n">
         <v>937.04</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>515.23K</t>
+          <t>591.09K</t>
         </is>
       </c>
       <c r="J289" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="290">

--- a/data/mk_inv_data_master.xlsx
+++ b/data/mk_inv_data_master.xlsx
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1512.61</v>
+        <v>1514.28</v>
       </c>
       <c r="F29" t="n">
         <v>1526.82</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>-0.0269</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="30">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223.51</v>
+        <v>223.67</v>
       </c>
       <c r="F31" t="n">
         <v>225.83</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>9.426</v>
+        <v>9.433999999999999</v>
       </c>
       <c r="F59" t="n">
         <v>9.512</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>-0.0276</v>
+        <v>-0.0267</v>
       </c>
     </row>
     <row r="60">
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>89.70999999999999</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F114" t="n">
         <v>91.28</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>-0.0174</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="115">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4367.3</v>
+        <v>4359.9</v>
       </c>
       <c r="F142" t="n">
         <v>4354.7</v>
@@ -5647,11 +5647,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>21.53K</t>
+          <t>22.26K</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>0.0072</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="143">
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>8064.01</v>
+        <v>8107.88</v>
       </c>
       <c r="F241" t="n">
         <v>7697.76</v>
@@ -9299,11 +9299,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>415.32K</t>
+          <t>429.37K</t>
         </is>
       </c>
       <c r="J241" t="n">
-        <v>0.0774</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="242">
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>1287.25</v>
+        <v>1294.88</v>
       </c>
       <c r="F265" t="n">
         <v>1221.75</v>
@@ -10257,11 +10257,11 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>185.58K</t>
+          <t>191.64K</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>0.0849</v>
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="266">
@@ -11202,7 +11202,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>965.79</v>
+        <v>968.37</v>
       </c>
       <c r="F289" t="n">
         <v>937.6900000000001</v>
@@ -11215,11 +11215,11 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>591.09K</t>
+          <t>608.17K</t>
         </is>
       </c>
       <c r="J289" t="n">
-        <v>0.0597</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="290">

--- a/data/mk_inv_data_master.xlsx
+++ b/data/mk_inv_data_master.xlsx
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1514.28</v>
+        <v>1516.52</v>
       </c>
       <c r="F29" t="n">
         <v>1526.82</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>-0.0259</v>
+        <v>-0.0244</v>
       </c>
     </row>
     <row r="30">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223.67</v>
+        <v>224.01</v>
       </c>
       <c r="F31" t="n">
         <v>225.83</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>9.433999999999999</v>
+        <v>9.449</v>
       </c>
       <c r="F59" t="n">
         <v>9.512</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>-0.0267</v>
+        <v>-0.0252</v>
       </c>
     </row>
     <row r="60">
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>89.98999999999999</v>
+        <v>89.92</v>
       </c>
       <c r="F114" t="n">
         <v>91.28</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>-0.0143</v>
+        <v>-0.0151</v>
       </c>
     </row>
     <row r="115">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4359.9</v>
+        <v>4361.3</v>
       </c>
       <c r="F142" t="n">
         <v>4354.7</v>
@@ -5647,11 +5647,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>22.26K</t>
+          <t>23.11K</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>0.0055</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="143">
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>8107.88</v>
+        <v>8096.93</v>
       </c>
       <c r="F241" t="n">
         <v>7697.76</v>
@@ -9299,11 +9299,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>429.37K</t>
+          <t>442.43K</t>
         </is>
       </c>
       <c r="J241" t="n">
-        <v>0.0833</v>
+        <v>0.0818</v>
       </c>
     </row>
     <row r="242">
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>1294.88</v>
+        <v>1293.4</v>
       </c>
       <c r="F265" t="n">
         <v>1221.75</v>
@@ -10257,11 +10257,11 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>191.64K</t>
+          <t>201.41K</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0901</v>
       </c>
     </row>
     <row r="266">
@@ -11202,7 +11202,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>968.37</v>
+        <v>967.8099999999999</v>
       </c>
       <c r="F289" t="n">
         <v>937.6900000000001</v>
@@ -11215,11 +11215,11 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>608.17K</t>
+          <t>615.19K</t>
         </is>
       </c>
       <c r="J289" t="n">
-        <v>0.0625</v>
+        <v>0.0619</v>
       </c>
     </row>
     <row r="290">
